--- a/tools/importer/reports/import-amazon-landing.report.xlsx
+++ b/tools/importer/reports/import-amazon-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
   <si>
     <t>_reportFile</t>
   </si>
@@ -59,6 +59,96 @@
   </si>
   <si>
     <t>https://choose.kaiserpermanente.org/amazon</t>
+  </si>
+  <si>
+    <t>amazon/getting-care.report.json</t>
+  </si>
+  <si>
+    <t>["hero-welcome","cards-resources","cards-resources"]</t>
+  </si>
+  <si>
+    <t>amazon/getting-care</t>
+  </si>
+  <si>
+    <t>2026-05-19T09:44:15.448Z</t>
+  </si>
+  <si>
+    <t>amazon Getting Care</t>
+  </si>
+  <si>
+    <t>https://choose.kaiserpermanente.org/amazon/getting-care</t>
+  </si>
+  <si>
+    <t>amazon/members-page.report.json</t>
+  </si>
+  <si>
+    <t>["hero-welcome","columns-coverage","columns-coverage","columns-coverage"]</t>
+  </si>
+  <si>
+    <t>amazon/members-page</t>
+  </si>
+  <si>
+    <t>2026-05-19T09:44:21.324Z</t>
+  </si>
+  <si>
+    <t>amazon Members Page</t>
+  </si>
+  <si>
+    <t>https://choose.kaiserpermanente.org/amazon/members-page</t>
+  </si>
+  <si>
+    <t>amazon/plans.report.json</t>
+  </si>
+  <si>
+    <t>["hero-welcome","columns-support","cards-resources"]</t>
+  </si>
+  <si>
+    <t>amazon/plans</t>
+  </si>
+  <si>
+    <t>2026-05-19T09:44:09.321Z</t>
+  </si>
+  <si>
+    <t>amazon Plans &amp; Benefits</t>
+  </si>
+  <si>
+    <t>https://choose.kaiserpermanente.org/amazon/plans</t>
+  </si>
+  <si>
+    <t>amazon/resources.report.json</t>
+  </si>
+  <si>
+    <t>["hero-welcome","cards-resources"]</t>
+  </si>
+  <si>
+    <t>amazon/resources</t>
+  </si>
+  <si>
+    <t>2026-05-19T09:44:03.218Z</t>
+  </si>
+  <si>
+    <t>amazon Open Enrollment Hub</t>
+  </si>
+  <si>
+    <t>https://choose.kaiserpermanente.org/amazon/resources</t>
+  </si>
+  <si>
+    <t>amazon/support.report.json</t>
+  </si>
+  <si>
+    <t>["hero-welcome"]</t>
+  </si>
+  <si>
+    <t>amazon/support</t>
+  </si>
+  <si>
+    <t>2026-05-19T09:44:26.800Z</t>
+  </si>
+  <si>
+    <t>amazon Support</t>
+  </si>
+  <si>
+    <t>https://choose.kaiserpermanente.org/amazon/support</t>
   </si>
 </sst>
 </file>
@@ -447,16 +537,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="44" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +599,136 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
